--- a/SGC-CKN/Excel/a2fe13dd-1df0-4c21-836d-af7de520142f_Cọc_khoan_nhồi_P7-152_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/a2fe13dd-1df0-4c21-836d-af7de520142f_Cọc_khoan_nhồi_P7-152_D800_17-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>18:40 17/03/2026</t>
+    <t>17:45 17/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -195,7 +195,7 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:55
+    <t xml:space="preserve">17:45
 17/03/2026</t>
   </si>
   <si>
@@ -365,12 +365,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -536,17 +536,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1241,53 +1241,53 @@
         <v>6.5</v>
       </c>
       <c r="G12" s="9">
-        <v>8.15</v>
+        <v>-8.5</v>
       </c>
       <c r="H12" s="9">
         <v>0.67</v>
       </c>
       <c r="I12" s="9">
-        <v>1.65</v>
-      </c>
-      <c r="J12" s="8">
-        <v>2.48</v>
+        <v>15</v>
+      </c>
+      <c r="J12" s="12">
+        <v>22.5</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="12">
-        <v>8.15</v>
-      </c>
-      <c r="G13" s="12">
-        <v>16.7</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="F13" s="13">
+        <v>-8.5</v>
+      </c>
+      <c r="G13" s="13">
+        <v>-16.7</v>
+      </c>
+      <c r="H13" s="13">
         <v>1.67</v>
       </c>
-      <c r="I13" s="12">
-        <v>8.55</v>
-      </c>
-      <c r="J13" s="15">
-        <v>5.13</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="I13" s="13">
+        <v>8.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>4.92</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="16">
-        <v>16.7</v>
+        <v>-16.7</v>
       </c>
       <c r="G14" s="16">
         <v>21</v>
@@ -1317,10 +1317,10 @@
         <v>0.5</v>
       </c>
       <c r="I14" s="16">
-        <v>4.3</v>
-      </c>
-      <c r="J14" s="15">
-        <v>8.6</v>
+        <v>37.7</v>
+      </c>
+      <c r="J14" s="12">
+        <v>75.4</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1389,7 +1389,7 @@
       <c r="I16" s="22">
         <v>10</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="12">
         <v>13.33</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1424,7 +1424,7 @@
       <c r="I17" s="25">
         <v>2.5</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="12">
         <v>6</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1494,7 +1494,7 @@
       <c r="I19" s="31">
         <v>4.1</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="12">
         <v>8.2</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1518,19 +1518,19 @@
         <v>57</v>
       </c>
       <c r="F20" s="34">
-        <v>43.2</v>
+        <v>-43.2</v>
       </c>
       <c r="G20" s="34">
         <v>44.89</v>
       </c>
       <c r="H20" s="34">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="I20" s="34">
-        <v>1.69</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2.25</v>
+        <v>88.09</v>
+      </c>
+      <c r="J20" s="12">
+        <v>151.01</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1717,45 +1717,45 @@
         <v>6.5</v>
       </c>
       <c r="F3" s="9">
-        <v>8.15</v>
+        <v>-8.5</v>
       </c>
       <c r="G3" s="9">
         <v>0.67</v>
       </c>
       <c r="H3" s="9">
-        <v>1.65</v>
-      </c>
-      <c r="I3" s="8">
-        <v>2.48</v>
+        <v>15</v>
+      </c>
+      <c r="I3" s="12">
+        <v>22.5</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
-        <v>8.15</v>
-      </c>
-      <c r="F4" s="12">
-        <v>16.7</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="E4" s="13">
+        <v>-8.5</v>
+      </c>
+      <c r="F4" s="13">
+        <v>-16.7</v>
+      </c>
+      <c r="G4" s="13">
         <v>1.67</v>
       </c>
-      <c r="H4" s="12">
-        <v>8.55</v>
-      </c>
-      <c r="I4" s="15">
-        <v>5.13</v>
+      <c r="H4" s="13">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>4.92</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>16.7</v>
+        <v>-16.7</v>
       </c>
       <c r="F5" s="16">
         <v>21</v>
@@ -1781,10 +1781,10 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="16">
-        <v>4.3</v>
-      </c>
-      <c r="I5" s="15">
-        <v>8.6</v>
+        <v>37.7</v>
+      </c>
+      <c r="I5" s="12">
+        <v>75.4</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1841,7 +1841,7 @@
       <c r="H7" s="22">
         <v>10</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="12">
         <v>13.33</v>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       <c r="H8" s="25">
         <v>2.5</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="12">
         <v>6</v>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       <c r="H10" s="31">
         <v>4.1</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="12">
         <v>8.2</v>
       </c>
     </row>
@@ -1946,19 +1946,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>43.2</v>
+        <v>-43.2</v>
       </c>
       <c r="F11" s="34">
         <v>44.89</v>
       </c>
       <c r="G11" s="34">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="34">
-        <v>1.69</v>
-      </c>
-      <c r="I11" s="8">
-        <v>2.25</v>
+        <v>88.09</v>
+      </c>
+      <c r="I11" s="12">
+        <v>151.01</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1981,13 +1981,13 @@
         <v>44.89</v>
       </c>
       <c r="G12" s="39">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="H12" s="39">
-        <v>44.89</v>
+        <v>177.69</v>
       </c>
       <c r="I12" s="39">
-        <v>5.55</v>
+        <v>22.45</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/a2fe13dd-1df0-4c21-836d-af7de520142f_Cọc_khoan_nhồi_P7-152_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/a2fe13dd-1df0-4c21-836d-af7de520142f_Cọc_khoan_nhồi_P7-152_D800_17-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:50
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
@@ -132,7 +132,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">14:10
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">15:00
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:45
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:10
@@ -172,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:40
@@ -182,9 +182,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">17:10
 17/03/2026</t>
   </si>
@@ -192,7 +189,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:45
@@ -1378,10 +1375,10 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="G16" s="22">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="H16" s="22">
         <v>0.75</v>
@@ -1413,10 +1410,10 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="G17" s="25">
-        <v>37.5</v>
+        <v>-37.5</v>
       </c>
       <c r="H17" s="25">
         <v>0.42</v>
@@ -1448,10 +1445,10 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>37.5</v>
+        <v>-37.5</v>
       </c>
       <c r="G18" s="28">
-        <v>39.1</v>
+        <v>-39.1</v>
       </c>
       <c r="H18" s="28">
         <v>0.5</v>
@@ -1474,19 +1471,19 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="31">
-        <v>39.1</v>
+        <v>-39.1</v>
       </c>
       <c r="G19" s="31">
-        <v>43.2</v>
+        <v>-43.2</v>
       </c>
       <c r="H19" s="31">
         <v>0.5</v>
@@ -1503,34 +1500,34 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>57</v>
       </c>
       <c r="F20" s="34">
         <v>-43.2</v>
       </c>
       <c r="G20" s="34">
-        <v>44.89</v>
+        <v>-44.89</v>
       </c>
       <c r="H20" s="34">
         <v>0.58</v>
       </c>
       <c r="I20" s="34">
-        <v>88.09</v>
-      </c>
-      <c r="J20" s="12">
-        <v>151.01</v>
+        <v>1.69</v>
+      </c>
+      <c r="J20" s="8">
+        <v>2.9</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1538,7 +1535,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1644,31 +1641,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1830,10 +1827,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="F7" s="22">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="G7" s="22">
         <v>0.75</v>
@@ -1859,10 +1856,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="F8" s="25">
-        <v>37.5</v>
+        <v>-37.5</v>
       </c>
       <c r="G8" s="25">
         <v>0.42</v>
@@ -1888,10 +1885,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>37.5</v>
+        <v>-37.5</v>
       </c>
       <c r="F9" s="28">
-        <v>39.1</v>
+        <v>-39.1</v>
       </c>
       <c r="G9" s="28">
         <v>0.5</v>
@@ -1911,16 +1908,16 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>39.1</v>
+        <v>-39.1</v>
       </c>
       <c r="F10" s="31">
-        <v>43.2</v>
+        <v>-43.2</v>
       </c>
       <c r="G10" s="31">
         <v>0.5</v>
@@ -1940,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1949,21 +1946,21 @@
         <v>-43.2</v>
       </c>
       <c r="F11" s="34">
-        <v>44.89</v>
+        <v>-44.89</v>
       </c>
       <c r="G11" s="34">
         <v>0.58</v>
       </c>
       <c r="H11" s="34">
-        <v>88.09</v>
-      </c>
-      <c r="I11" s="12">
-        <v>151.01</v>
+        <v>1.69</v>
+      </c>
+      <c r="I11" s="8">
+        <v>2.9</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1978,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>44.89</v>
+        <v>-44.89</v>
       </c>
       <c r="G12" s="39">
         <v>7.92</v>
       </c>
       <c r="H12" s="39">
-        <v>177.69</v>
+        <v>91.29</v>
       </c>
       <c r="I12" s="39">
-        <v>22.45</v>
+        <v>11.53</v>
       </c>
     </row>
   </sheetData>
